--- a/Bandra_September_2026_Reports_4-9_Data.xlsx
+++ b/Bandra_September_2026_Reports_4-9_Data.xlsx
@@ -1,69 +1,69 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Three Septembers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Format matrix Sep-26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Format matrix Sep-25" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Members per format Sep-26" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 Core vs new members" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Member frequency Sep-26" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 The returning core, top 20" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Booking book" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Room size Sep-26" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 Complimentary seats" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Acquisition sources" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 First purchase to LTV" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 Speed to second visit" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 Visit funnel" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15 Buyer concentration" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16 Payment method Sep-26" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17 Late cancellations by year" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18 Cancellation concentration" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19 Cancellations by format" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20 Cancellations by day" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21 Discount by year" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22 Discount by product" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23 Discount by seller" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24 Discount effectiveness" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25 Membership survival" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26 Membership duration bands" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27 Product renewal" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28 Unused credit" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29 Winnability by recency" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30 Cancellation bands" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31 Lead sources" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32 Follow-up contact" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33 Trainer scorecard" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34 Matched slots" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35 Teaching month by month" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36 Teaching by discipline" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37 The member base" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38 Multi-format ladder" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40 Member frequency 2026" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39 Lead channels" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41 Product book" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42 Lead handling" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43 Lead flow 2026" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44 Lead channels" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45 Lead funnel" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46 The trial gate" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47 Enquiry to purchase" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48 The open file" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49 2026 lead cohorts" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50 Member frequency" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="51 Gap between visits" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="52 Gap between purchases" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="53 Sales by hour" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="54 Sales by day of month" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="55 Visit number curve" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="56 Frequency by month" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01 Three Septembers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02 Format matrix Sep-26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03 Format matrix Sep-25" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04 Members per format Sep-26" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05 Core vs new members" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06 Member frequency Sep-26" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07 The returning core, top 20" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08 Booking book" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09 Room size Sep-26" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10 Complimentary seats" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11 Acquisition sources" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12 First purchase to LTV" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="13 Speed to second visit" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14 Visit funnel" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="15 Buyer concentration" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="16 Payment method Sep-26" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="17 Late cancellations by year" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="18 Cancellation concentration" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="19 Cancellations by format" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="20 Cancellations by day" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="21 Discount by year" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="22 Discount by product" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="23 Discount by seller" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="24 Discount effectiveness" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="25 Membership survival" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="26 Membership duration bands" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="27 Product renewal" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="28 Unused credit" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="29 Winnability by recency" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="30 Cancellation bands" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="31 Lead sources" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="32 Follow-up contact" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="33 Trainer scorecard" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="34 Matched slots" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="35 Teaching month by month" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="36 Teaching by discipline" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="37 The member base" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="38 Multi-format ladder" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="40 Member frequency 2026" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="39 Lead channels" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="41 Product book" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="42 Lead handling" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="43 Lead flow 2026" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="44 Lead channels" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="45 Lead funnel" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="46 The trial gate" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="47 Enquiry to purchase" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="48 The open file" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="49 2026 lead cohorts" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="50 Member frequency" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="51 Gap between visits" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="52 Gap between purchases" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="53 Sales by hour" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="54 Sales by day of month" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="55 Visit number curve" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="56 Frequency by month" sheetId="57" state="visible" r:id="rId57"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1,017 people bought something in the twelve months to 30 September 2026.</t>
+          <t>1,015 people bought something in the twelve months to 30 September 2026.</t>
         </is>
       </c>
     </row>
@@ -1572,10 +1572,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C2" t="n">
         <v>3.7</v>
@@ -1637,13 +1637,13 @@
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>924</v>
+        <v>898</v>
       </c>
       <c r="F2" t="n">
-        <v>1.494423791821561</v>
+        <v>1.460674157303371</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3676951672862454</v>
+        <v>0.3634831460674157</v>
       </c>
     </row>
     <row r="3">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C3" t="n">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>6152</v>
+        <v>5855</v>
       </c>
       <c r="F3" t="n">
-        <v>5.25390625</v>
+        <v>5.027888446215139</v>
       </c>
       <c r="G3" t="n">
-        <v>1.956328125</v>
+        <v>1.945179282868526</v>
       </c>
     </row>
     <row r="4">
@@ -1678,22 +1678,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C4" t="n">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>10369</v>
+        <v>10099</v>
       </c>
       <c r="F4" t="n">
-        <v>6.859649122807017</v>
+        <v>6.373493975903615</v>
       </c>
       <c r="G4" t="n">
-        <v>2.498479532163743</v>
+        <v>2.419578313253012</v>
       </c>
     </row>
     <row r="5">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C5" t="n">
-        <v>25.6</v>
+        <v>26.2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>8280</v>
+        <v>8154</v>
       </c>
       <c r="F5" t="n">
-        <v>6.646616541353383</v>
+        <v>6.538461538461538</v>
       </c>
       <c r="G5" t="n">
-        <v>2.501052631578947</v>
+        <v>2.450230769230769</v>
       </c>
     </row>
     <row r="6">
@@ -1753,22 +1753,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>12678</v>
+        <v>12712</v>
       </c>
       <c r="F7" t="n">
-        <v>8.984848484848484</v>
+        <v>9.123076923076923</v>
       </c>
       <c r="G7" t="n">
-        <v>2.71969696969697</v>
+        <v>2.761538461538461</v>
       </c>
     </row>
     <row r="8">
@@ -1794,56 +1794,6 @@
       </c>
       <c r="G8" t="n">
         <v>3.858148148148148</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Abandoned checkout</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>23</v>
-      </c>
-      <c r="C9" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1629</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.782608695652174</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.022608695652174</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>23</v>
-      </c>
-      <c r="C10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>9</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7439</v>
-      </c>
-      <c r="F10" t="n">
-        <v>7.521739130434782</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.867391304347826</v>
       </c>
     </row>
   </sheetData>
@@ -2386,7 +2336,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="4">
@@ -2422,11 +2372,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>all 517 others</t>
+          <t>all 515 others</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3302,7 +3252,7 @@
         <v>2024</v>
       </c>
       <c r="B2" t="n">
-        <v>1520</v>
+        <v>1408</v>
       </c>
       <c r="C2" t="n">
         <v>11798069</v>
@@ -3317,7 +3267,7 @@
         <v>7.99</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="3">
@@ -3325,22 +3275,22 @@
         <v>2025</v>
       </c>
       <c r="B3" t="n">
-        <v>2885</v>
+        <v>2546</v>
       </c>
       <c r="C3" t="n">
-        <v>22136598</v>
+        <v>22032923</v>
       </c>
       <c r="D3" t="n">
-        <v>2001996</v>
+        <v>1906586</v>
       </c>
       <c r="E3" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F3" t="n">
-        <v>9.039999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="4">
@@ -3348,22 +3298,22 @@
         <v>2026</v>
       </c>
       <c r="B4" t="n">
-        <v>2142</v>
+        <v>1905</v>
       </c>
       <c r="C4" t="n">
-        <v>19309890</v>
+        <v>18747882</v>
       </c>
       <c r="D4" t="n">
-        <v>2557453</v>
+        <v>1999121</v>
       </c>
       <c r="E4" t="n">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F4" t="n">
-        <v>13.24</v>
+        <v>10.66</v>
       </c>
       <c r="G4" t="n">
-        <v>18.4</v>
+        <v>20.5</v>
       </c>
     </row>
   </sheetData>
@@ -3429,101 +3379,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Studio 1 Month Unlimited</t>
+          <t>Studio 3 Month Unlimited</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>185</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>3804389</v>
+        <v>2070495</v>
       </c>
       <c r="D2" t="n">
-        <v>823219</v>
+        <v>337091</v>
       </c>
       <c r="E2" t="n">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="F2" t="n">
-        <v>21.6</v>
+        <v>16.3</v>
       </c>
       <c r="G2" t="n">
-        <v>67.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Studio 3 Month Unlimited</t>
+          <t>Studio 1 Month Unlimited</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>170</v>
       </c>
       <c r="C3" t="n">
-        <v>2117097</v>
+        <v>3453432</v>
       </c>
       <c r="D3" t="n">
-        <v>383693</v>
+        <v>472262</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="F3" t="n">
-        <v>18.1</v>
+        <v>13.7</v>
       </c>
       <c r="G3" t="n">
-        <v>74.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Studio 10 Class Package</t>
+          <t>Studio 6 Month Unlimited</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>1599969</v>
+        <v>1588098</v>
       </c>
       <c r="D4" t="n">
-        <v>208600</v>
+        <v>197932</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="G4" t="n">
-        <v>94.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Studio 6 Month Unlimited</t>
+          <t>Studio 10 Class Package</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="C5" t="n">
-        <v>1588098</v>
+        <v>1528969</v>
       </c>
       <c r="D5" t="n">
-        <v>197932</v>
+        <v>137600</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>118.9</v>
       </c>
     </row>
     <row r="6">
@@ -3533,7 +3483,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C6" t="n">
         <v>2534448</v>
@@ -3548,7 +3498,7 @@
         <v>6.4</v>
       </c>
       <c r="G6" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="7">
@@ -3583,10 +3533,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C8" t="n">
-        <v>523391</v>
+        <v>519716</v>
       </c>
       <c r="D8" t="n">
         <v>5688</v>
@@ -3608,7 +3558,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="C9" t="n">
         <v>680124</v>
@@ -3658,7 +3608,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>61671</v>
@@ -3683,7 +3633,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="C12" t="n">
         <v>44660</v>
@@ -3708,7 +3658,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="C13" t="n">
         <v>134365</v>
@@ -3758,7 +3708,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="C15" t="n">
         <v>574665</v>
@@ -3843,22 +3793,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>463</v>
+        <v>387</v>
       </c>
       <c r="C2" t="n">
-        <v>3499761</v>
+        <v>3330188</v>
       </c>
       <c r="D2" t="n">
-        <v>602435</v>
+        <v>432862</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>17.2</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="3">
@@ -3868,22 +3818,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>595</v>
+        <v>520</v>
       </c>
       <c r="C3" t="n">
-        <v>3804899</v>
+        <v>3567402</v>
       </c>
       <c r="D3" t="n">
-        <v>629032</v>
+        <v>393372</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>16.8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -3893,22 +3843,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="C4" t="n">
-        <v>3292046</v>
+        <v>3230297</v>
       </c>
       <c r="D4" t="n">
-        <v>409521</v>
+        <v>347772</v>
       </c>
       <c r="E4" t="n">
         <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>12.4</v>
+        <v>10.8</v>
       </c>
       <c r="G4" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="5">
@@ -3918,22 +3868,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="C5" t="n">
-        <v>4329126</v>
+        <v>4235939</v>
       </c>
       <c r="D5" t="n">
-        <v>529500</v>
+        <v>438150</v>
       </c>
       <c r="E5" t="n">
         <v>104</v>
       </c>
       <c r="F5" t="n">
-        <v>12.2</v>
+        <v>10.3</v>
       </c>
       <c r="G5" t="n">
-        <v>27.9</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="6">
@@ -3943,7 +3893,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C6" t="n">
         <v>4069738</v>
@@ -3958,7 +3908,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
     </row>
   </sheetData>
@@ -4036,7 +3986,7 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>17841</v>
+        <v>17833</v>
       </c>
     </row>
     <row r="3">
@@ -4057,10 +4007,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="F3" t="n">
-        <v>62483</v>
+        <v>62478</v>
       </c>
     </row>
     <row r="4">
@@ -4081,10 +4031,10 @@
         <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="F4" t="n">
-        <v>17314</v>
+        <v>17311</v>
       </c>
     </row>
     <row r="5">
@@ -4129,10 +4079,10 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>8.52</v>
+        <v>8.5</v>
       </c>
       <c r="F6" t="n">
-        <v>102470</v>
+        <v>102439</v>
       </c>
     </row>
     <row r="7">
@@ -4153,10 +4103,10 @@
         <v>77.3</v>
       </c>
       <c r="E7" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="F7" t="n">
-        <v>54975</v>
+        <v>54953</v>
       </c>
     </row>
     <row r="8">
@@ -4171,16 +4121,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8" t="n">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>9.529999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>107053</v>
+        <v>111824</v>
       </c>
     </row>
     <row r="9">
@@ -4195,16 +4145,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>5.12</v>
+        <v>4.99</v>
       </c>
       <c r="F9" t="n">
-        <v>80308</v>
+        <v>78736</v>
       </c>
     </row>
     <row r="10">
@@ -4249,10 +4199,10 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>6.67</v>
+        <v>6.33</v>
       </c>
       <c r="F11" t="n">
-        <v>29250</v>
+        <v>28660</v>
       </c>
     </row>
   </sheetData>
@@ -12317,7 +12267,7 @@
         <v>5043</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -12361,7 +12311,7 @@
         <v>4989</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -12383,7 +12333,7 @@
         <v>4608</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -14269,7 +14219,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2883</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="3">
@@ -14279,7 +14229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="4">
@@ -14299,7 +14249,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6">
@@ -14319,7 +14269,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -14451,10 +14401,10 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C10" t="n">
-        <v>1224640</v>
+        <v>1222802</v>
       </c>
     </row>
     <row r="11">
@@ -14495,10 +14445,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C14" t="n">
-        <v>700324</v>
+        <v>698486</v>
       </c>
     </row>
     <row r="15">
@@ -14696,10 +14646,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>289909</v>
+        <v>288072</v>
       </c>
     </row>
     <row r="8">
@@ -14883,10 +14833,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C24" t="n">
-        <v>529464</v>
+        <v>527626</v>
       </c>
     </row>
     <row r="25">
